--- a/config/tests/2_test_orientacion_especialidades.xlsx
+++ b/config/tests/2_test_orientacion_especialidades.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,18 @@
       <c r="B2" t="inlineStr">
         <is>
           <t>Orientación para especialidades en Administración</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>instrucciones</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Indica el nivel de apoyo que necesitas para realizar cada actividad considerando tus experiencias del último año.</t>
         </is>
       </c>
     </row>

--- a/config/tests/2_test_orientacion_especialidades.xlsx
+++ b/config/tests/2_test_orientacion_especialidades.xlsx
@@ -11,6 +11,7 @@
     <sheet name="especialidades" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="preguntas" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="escala" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="niveles" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1358,4 +1359,80 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ambito</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>minimo</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>etiqueta</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ALTO (Perfil Fuerte)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MEDIO (En Desarrollo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BAJO (Baja Afinidad)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/config/tests/2_test_orientacion_especialidades.xlsx
+++ b/config/tests/2_test_orientacion_especialidades.xlsx
@@ -440,7 +440,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Orientación para especialidades en Administración</t>
+          <t>Test 2: Administration Specialties</t>
         </is>
       </c>
     </row>
